--- a/Assets/Resources/物品数据.xlsx
+++ b/Assets/Resources/物品数据.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SCP Completely out of control\Assets\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9432031D-0889-4330-B2D7-F58E1ED0DA9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A781CB72-B125-4F27-8A5B-A0B92EEDBB02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3870" yWindow="4680" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>物品名称</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -98,18 +98,6 @@
   </si>
   <si>
     <t>(test)占位物体6</t>
-  </si>
-  <si>
-    <t>(test)占位物体7</t>
-  </si>
-  <si>
-    <t>(test)占位物体8</t>
-  </si>
-  <si>
-    <t>(test)占位物体9</t>
-  </si>
-  <si>
-    <t>(test)占位物体10</t>
   </si>
 </sst>
 </file>
@@ -139,7 +127,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -155,6 +143,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -188,24 +182,27 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -475,248 +472,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="1"/>
-    <col min="2" max="2" width="18" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="17" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
+    <col min="1" max="1" width="9" style="5"/>
+    <col min="2" max="2" width="18" style="5" customWidth="1"/>
+    <col min="3" max="3" width="9" style="5"/>
+    <col min="4" max="4" width="17" style="5" customWidth="1"/>
+    <col min="5" max="5" width="13.08984375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="19.6328125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A4" s="1">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
         <v>10000</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="5">
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A5" s="1">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
         <v>10001</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="5">
         <v>0</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A6" s="1">
+      <c r="E5" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
         <v>10002</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="5">
         <v>0</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A7" s="1">
+      <c r="E6" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
         <v>10003</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="5">
         <v>0</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A8" s="1">
+      <c r="E7" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
         <v>10004</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="5">
         <v>0</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A9" s="1">
+      <c r="E8" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
         <v>10005</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="5">
         <v>0</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A10" s="1">
-        <v>10006</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A11" s="1">
-        <v>10007</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A12" s="1">
-        <v>10008</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="A13" s="1">
-        <v>10009</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B14" s="4"/>
+      <c r="E9" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="3"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="3"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="3"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -728,7 +669,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -739,7 +680,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
